--- a/assets/starter-pack/rebuilt/FLK_09_Capture_Maturity_Self_Audit.xlsx
+++ b/assets/starter-pack/rebuilt/FLK_09_Capture_Maturity_Self_Audit.xlsx
@@ -4,18 +4,85 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Self-Audit" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Score Dashboard" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Action Plan" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Help &amp; Examples" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Self-Audit" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Score Dashboard" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Action Plan" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Help &amp; Examples" state="visible" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="MaturityScore">Lists!$A$2:$A$6</definedName>
+    <definedName name="ActionWindow">Lists!$B$2:$B$4</definedName>
+    <definedName name="PriorityLevel">Lists!$C$2:$C$5</definedName>
+    <definedName name="TaskStatus">Lists!$D$2:$D$5</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="220">
+  <si>
+    <t>Maturity Score (0-4)</t>
+  </si>
+  <si>
+    <t>Action Window</t>
+  </si>
+  <si>
+    <t>Priority Level</t>
+  </si>
+  <si>
+    <t>Task Status</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>30 days</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>60 days</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>90 days</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
   <si>
     <t>CAPTURE MATURITY SELF-AUDIT — INSTRUCTIONS</t>
   </si>
@@ -446,15 +513,6 @@
     <t>Market Intelligence</t>
   </si>
   <si>
-    <t>30 days</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
     <t>Pull FPDS data on top 5 incumbent contracts in our space</t>
   </si>
   <si>
@@ -464,9 +522,6 @@
     <t>Compliance</t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
     <t>Create a one-page pipeline tracker with PWin scores per pursuit</t>
   </si>
   <si>
@@ -488,9 +543,6 @@
     <t>Relationships</t>
   </si>
   <si>
-    <t>60 days</t>
-  </si>
-  <si>
     <t>Write 3 structured past performance references in CPARS format</t>
   </si>
   <si>
@@ -500,9 +552,6 @@
     <t>Pull competitor labor rates from GSA CALC for top 5 categories</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>Template your standard proposal outline mapped to Section L and M</t>
   </si>
   <si>
@@ -518,9 +567,6 @@
     <t>Run a Pink team internal review on the next live proposal</t>
   </si>
   <si>
-    <t>90 days</t>
-  </si>
-  <si>
     <t>Debrief win / loss on the last 3 submitted proposals</t>
   </si>
   <si>
@@ -546,9 +592,6 @@
   </si>
   <si>
     <t>In progress</t>
-  </si>
-  <si>
-    <t>Blocked</t>
   </si>
   <si>
     <t>Not started</t>
@@ -649,12 +692,21 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -695,12 +747,17 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -765,90 +822,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2247,6 +2310,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2260,143 +2409,143 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3"/>
     </row>
     <row r="3" ht="48" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
+      <c r="B5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="64" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>10</v>
+      <c r="B7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>12</v>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="64" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="64" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>16</v>
+      <c r="B10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>18</v>
+      <c r="B11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1"/>
+      <c r="B13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>23</v>
+      <c r="B15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
+      <c r="B16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>27</v>
+      <c r="B17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>29</v>
+      <c r="B18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>31</v>
+      <c r="B19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>33</v>
+      <c r="B20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2413,7 +2562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2432,1218 +2581,1218 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="B2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
+      <c r="B3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="B4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="B5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="11">
         <v>0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>4</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="13">
         <f>IFERROR(C5/D5,0)</f>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="12">
         <f>IF(C5=0,"Missing",IF(C5=1,"Aware",IF(C5=2,"Partial",IF(C5=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="12">
         <f>IF(C5&lt;=1,"FIX",IF(C5=2,"Improve",""))</f>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>45</v>
+      <c r="H5" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="B6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="11">
         <v>0</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <v>4</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="13">
         <f>IFERROR(C6/D6,0)</f>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <f>IF(C6=0,"Missing",IF(C6=1,"Aware",IF(C6=2,"Partial",IF(C6=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="12">
         <f>IF(C6&lt;=1,"FIX",IF(C6=2,"Improve",""))</f>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>45</v>
+      <c r="H6" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="11">
         <v>0</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>4</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="13">
         <f>IFERROR(C7/D7,0)</f>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="12">
         <f>IF(C7=0,"Missing",IF(C7=1,"Aware",IF(C7=2,"Partial",IF(C7=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="12">
         <f>IF(C7&lt;=1,"FIX",IF(C7=2,"Improve",""))</f>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>45</v>
+      <c r="H7" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="B8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="11">
         <v>0</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <v>4</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="13">
         <f>IFERROR(C8/D8,0)</f>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="12">
         <f>IF(C8=0,"Missing",IF(C8=1,"Aware",IF(C8=2,"Partial",IF(C8=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="12">
         <f>IF(C8&lt;=1,"FIX",IF(C8=2,"Improve",""))</f>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>45</v>
+      <c r="H8" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="9">
+      <c r="B9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="11">
         <v>0</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="12">
         <v>4</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="13">
         <f>IFERROR(C9/D9,0)</f>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="12">
         <f>IF(C9=0,"Missing",IF(C9=1,"Aware",IF(C9=2,"Partial",IF(C9=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="12">
         <f>IF(C9&lt;=1,"FIX",IF(C9=2,"Improve",""))</f>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>45</v>
+      <c r="H9" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="9">
+      <c r="B10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="11">
         <v>0</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="12">
         <v>4</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="13">
         <f>IFERROR(C10/D10,0)</f>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="12">
         <f>IF(C10=0,"Missing",IF(C10=1,"Aware",IF(C10=2,"Partial",IF(C10=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="12">
         <f>IF(C10&lt;=1,"FIX",IF(C10=2,"Improve",""))</f>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>45</v>
+      <c r="H10" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="13">
+      <c r="B11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="15">
         <f>SUM(C5:C10)</f>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="15">
         <f>SUM(D5:D10)</f>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="16">
         <f>IFERROR(C11/D11,0)</f>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="15">
         <f>IF(E11&gt;=0.85,"Optimized",IF(E11&gt;=0.70,"Strong",IF(E11&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="15">
         <f>IF(E11&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>45</v>
+      <c r="H11" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="B12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="9">
+      <c r="B13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="11">
         <v>0</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="12">
         <v>4</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="13">
         <f>IFERROR(C13/D13,0)</f>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="12">
         <f>IF(C13=0,"Missing",IF(C13=1,"Aware",IF(C13=2,"Partial",IF(C13=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="12">
         <f>IF(C13&lt;=1,"FIX",IF(C13=2,"Improve",""))</f>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>45</v>
+      <c r="H13" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="9">
+      <c r="B14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="11">
         <v>0</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="12">
         <v>4</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="13">
         <f>IFERROR(C14/D14,0)</f>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="12">
         <f>IF(C14=0,"Missing",IF(C14=1,"Aware",IF(C14=2,"Partial",IF(C14=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="12">
         <f>IF(C14&lt;=1,"FIX",IF(C14=2,"Improve",""))</f>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>45</v>
+      <c r="H14" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="9">
+      <c r="B15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="11">
         <v>0</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="12">
         <v>4</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="13">
         <f>IFERROR(C15/D15,0)</f>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="12">
         <f>IF(C15=0,"Missing",IF(C15=1,"Aware",IF(C15=2,"Partial",IF(C15=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="12">
         <f>IF(C15&lt;=1,"FIX",IF(C15=2,"Improve",""))</f>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>45</v>
+      <c r="H15" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B16" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="11">
         <v>0</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="12">
         <v>4</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="13">
         <f>IFERROR(C16/D16,0)</f>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="12">
         <f>IF(C16=0,"Missing",IF(C16=1,"Aware",IF(C16=2,"Partial",IF(C16=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="12">
         <f>IF(C16&lt;=1,"FIX",IF(C16=2,"Improve",""))</f>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>45</v>
+      <c r="H16" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="B17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="11">
         <v>0</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="12">
         <v>4</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="13">
         <f>IFERROR(C17/D17,0)</f>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="12">
         <f>IF(C17=0,"Missing",IF(C17=1,"Aware",IF(C17=2,"Partial",IF(C17=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="12">
         <f>IF(C17&lt;=1,"FIX",IF(C17=2,"Improve",""))</f>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>45</v>
+      <c r="H17" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="9">
+      <c r="B18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="11">
         <v>0</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="12">
         <v>4</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="13">
         <f>IFERROR(C18/D18,0)</f>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="12">
         <f>IF(C18=0,"Missing",IF(C18=1,"Aware",IF(C18=2,"Partial",IF(C18=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="12">
         <f>IF(C18&lt;=1,"FIX",IF(C18=2,"Improve",""))</f>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>45</v>
+      <c r="H18" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="13">
+      <c r="B19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="15">
         <f>SUM(C13:C18)</f>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="15">
         <f>SUM(D13:D18)</f>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="16">
         <f>IFERROR(C19/D19,0)</f>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="15">
         <f>IF(E19&gt;=0.85,"Optimized",IF(E19&gt;=0.70,"Strong",IF(E19&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="15">
         <f>IF(E19&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H19" s="15" t="s">
-        <v>45</v>
+      <c r="H19" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="B20" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="11">
         <v>0</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="12">
         <v>4</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="13">
         <f>IFERROR(C21/D21,0)</f>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="12">
         <f>IF(C21=0,"Missing",IF(C21=1,"Aware",IF(C21=2,"Partial",IF(C21=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="12">
         <f>IF(C21&lt;=1,"FIX",IF(C21=2,"Improve",""))</f>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>45</v>
+      <c r="H21" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="B22" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="11">
         <v>0</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="12">
         <v>4</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="13">
         <f>IFERROR(C22/D22,0)</f>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <f>IF(C22=0,"Missing",IF(C22=1,"Aware",IF(C22=2,"Partial",IF(C22=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="12">
         <f>IF(C22&lt;=1,"FIX",IF(C22=2,"Improve",""))</f>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>45</v>
+      <c r="H22" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="B23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="11">
         <v>0</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="12">
         <v>4</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="13">
         <f>IFERROR(C23/D23,0)</f>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="12">
         <f>IF(C23=0,"Missing",IF(C23=1,"Aware",IF(C23=2,"Partial",IF(C23=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="12">
         <f>IF(C23&lt;=1,"FIX",IF(C23=2,"Improve",""))</f>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>45</v>
+      <c r="H23" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="9">
+      <c r="B24" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="11">
         <v>0</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="12">
         <v>4</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="13">
         <f>IFERROR(C24/D24,0)</f>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="12">
         <f>IF(C24=0,"Missing",IF(C24=1,"Aware",IF(C24=2,"Partial",IF(C24=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="12">
         <f>IF(C24&lt;=1,"FIX",IF(C24=2,"Improve",""))</f>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>45</v>
+      <c r="H24" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="9">
+      <c r="B25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="11">
         <v>0</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="12">
         <v>4</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="13">
         <f>IFERROR(C25/D25,0)</f>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="12">
         <f>IF(C25=0,"Missing",IF(C25=1,"Aware",IF(C25=2,"Partial",IF(C25=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="12">
         <f>IF(C25&lt;=1,"FIX",IF(C25=2,"Improve",""))</f>
       </c>
-      <c r="H25" s="12" t="s">
-        <v>45</v>
+      <c r="H25" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="9">
+      <c r="B26" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="11">
         <v>0</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="12">
         <v>4</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="13">
         <f>IFERROR(C26/D26,0)</f>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="12">
         <f>IF(C26=0,"Missing",IF(C26=1,"Aware",IF(C26=2,"Partial",IF(C26=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="12">
         <f>IF(C26&lt;=1,"FIX",IF(C26=2,"Improve",""))</f>
       </c>
-      <c r="H26" s="12" t="s">
-        <v>45</v>
+      <c r="H26" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="13">
+      <c r="B27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="15">
         <f>SUM(C21:C26)</f>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="15">
         <f>SUM(D21:D26)</f>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="16">
         <f>IFERROR(C27/D27,0)</f>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="15">
         <f>IF(E27&gt;=0.85,"Optimized",IF(E27&gt;=0.70,"Strong",IF(E27&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="15">
         <f>IF(E27&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H27" s="15" t="s">
-        <v>45</v>
+      <c r="H27" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="B28" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="9">
+      <c r="B29" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="11">
         <v>0</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="12">
         <v>4</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="13">
         <f>IFERROR(C29/D29,0)</f>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="12">
         <f>IF(C29=0,"Missing",IF(C29=1,"Aware",IF(C29=2,"Partial",IF(C29=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="12">
         <f>IF(C29&lt;=1,"FIX",IF(C29=2,"Improve",""))</f>
       </c>
-      <c r="H29" s="12" t="s">
-        <v>45</v>
+      <c r="H29" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="9">
+      <c r="B30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="11">
         <v>0</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="12">
         <v>4</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="13">
         <f>IFERROR(C30/D30,0)</f>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="12">
         <f>IF(C30=0,"Missing",IF(C30=1,"Aware",IF(C30=2,"Partial",IF(C30=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="12">
         <f>IF(C30&lt;=1,"FIX",IF(C30=2,"Improve",""))</f>
       </c>
-      <c r="H30" s="12" t="s">
-        <v>45</v>
+      <c r="H30" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="9">
+      <c r="B31" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="11">
         <v>0</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="12">
         <v>4</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="13">
         <f>IFERROR(C31/D31,0)</f>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="12">
         <f>IF(C31=0,"Missing",IF(C31=1,"Aware",IF(C31=2,"Partial",IF(C31=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="12">
         <f>IF(C31&lt;=1,"FIX",IF(C31=2,"Improve",""))</f>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>45</v>
+      <c r="H31" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="9">
+      <c r="B32" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="11">
         <v>0</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="12">
         <v>4</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="13">
         <f>IFERROR(C32/D32,0)</f>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="12">
         <f>IF(C32=0,"Missing",IF(C32=1,"Aware",IF(C32=2,"Partial",IF(C32=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="12">
         <f>IF(C32&lt;=1,"FIX",IF(C32=2,"Improve",""))</f>
       </c>
-      <c r="H32" s="12" t="s">
-        <v>45</v>
+      <c r="H32" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="9">
+      <c r="B33" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="11">
         <v>0</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="12">
         <v>4</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="13">
         <f>IFERROR(C33/D33,0)</f>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="12">
         <f>IF(C33=0,"Missing",IF(C33=1,"Aware",IF(C33=2,"Partial",IF(C33=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="12">
         <f>IF(C33&lt;=1,"FIX",IF(C33=2,"Improve",""))</f>
       </c>
-      <c r="H33" s="12" t="s">
-        <v>45</v>
+      <c r="H33" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="9">
+      <c r="B34" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="11">
         <v>0</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="12">
         <v>4</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="13">
         <f>IFERROR(C34/D34,0)</f>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="12">
         <f>IF(C34=0,"Missing",IF(C34=1,"Aware",IF(C34=2,"Partial",IF(C34=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="12">
         <f>IF(C34&lt;=1,"FIX",IF(C34=2,"Improve",""))</f>
       </c>
-      <c r="H34" s="12" t="s">
-        <v>45</v>
+      <c r="H34" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="13">
+      <c r="B35" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="15">
         <f>SUM(C29:C34)</f>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="15">
         <f>SUM(D29:D34)</f>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="16">
         <f>IFERROR(C35/D35,0)</f>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="15">
         <f>IF(E35&gt;=0.85,"Optimized",IF(E35&gt;=0.70,"Strong",IF(E35&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="15">
         <f>IF(E35&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H35" s="15" t="s">
-        <v>45</v>
+      <c r="H35" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="B36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" s="9">
+      <c r="B37" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="11">
         <v>0</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="12">
         <v>4</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="13">
         <f>IFERROR(C37/D37,0)</f>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="12">
         <f>IF(C37=0,"Missing",IF(C37=1,"Aware",IF(C37=2,"Partial",IF(C37=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="12">
         <f>IF(C37&lt;=1,"FIX",IF(C37=2,"Improve",""))</f>
       </c>
-      <c r="H37" s="12" t="s">
-        <v>45</v>
+      <c r="H37" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="9">
+      <c r="B38" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="11">
         <v>0</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="12">
         <v>4</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="13">
         <f>IFERROR(C38/D38,0)</f>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="12">
         <f>IF(C38=0,"Missing",IF(C38=1,"Aware",IF(C38=2,"Partial",IF(C38=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="12">
         <f>IF(C38&lt;=1,"FIX",IF(C38=2,"Improve",""))</f>
       </c>
-      <c r="H38" s="12" t="s">
-        <v>45</v>
+      <c r="H38" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="9">
+      <c r="B39" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="11">
         <v>0</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="12">
         <v>4</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="13">
         <f>IFERROR(C39/D39,0)</f>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="12">
         <f>IF(C39=0,"Missing",IF(C39=1,"Aware",IF(C39=2,"Partial",IF(C39=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="12">
         <f>IF(C39&lt;=1,"FIX",IF(C39=2,"Improve",""))</f>
       </c>
-      <c r="H39" s="12" t="s">
-        <v>45</v>
+      <c r="H39" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="9">
+      <c r="B40" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="11">
         <v>0</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="12">
         <v>4</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="13">
         <f>IFERROR(C40/D40,0)</f>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="12">
         <f>IF(C40=0,"Missing",IF(C40=1,"Aware",IF(C40=2,"Partial",IF(C40=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="12">
         <f>IF(C40&lt;=1,"FIX",IF(C40=2,"Improve",""))</f>
       </c>
-      <c r="H40" s="12" t="s">
-        <v>45</v>
+      <c r="H40" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="9">
+      <c r="B41" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="11">
         <v>0</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="12">
         <v>4</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="13">
         <f>IFERROR(C41/D41,0)</f>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="12">
         <f>IF(C41=0,"Missing",IF(C41=1,"Aware",IF(C41=2,"Partial",IF(C41=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="12">
         <f>IF(C41&lt;=1,"FIX",IF(C41=2,"Improve",""))</f>
       </c>
-      <c r="H41" s="12" t="s">
-        <v>45</v>
+      <c r="H41" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="9">
+      <c r="B42" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="11">
         <v>0</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="12">
         <v>4</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="13">
         <f>IFERROR(C42/D42,0)</f>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="12">
         <f>IF(C42=0,"Missing",IF(C42=1,"Aware",IF(C42=2,"Partial",IF(C42=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="12">
         <f>IF(C42&lt;=1,"FIX",IF(C42=2,"Improve",""))</f>
       </c>
-      <c r="H42" s="12" t="s">
-        <v>45</v>
+      <c r="H42" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="13">
+      <c r="B43" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="15">
         <f>SUM(C37:C42)</f>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="15">
         <f>SUM(D37:D42)</f>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="16">
         <f>IFERROR(C43/D43,0)</f>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="15">
         <f>IF(E43&gt;=0.85,"Optimized",IF(E43&gt;=0.70,"Strong",IF(E43&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="15">
         <f>IF(E43&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H43" s="15" t="s">
-        <v>45</v>
+      <c r="H43" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+      <c r="B44" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
     </row>
     <row r="45" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" s="9">
+      <c r="B45" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="11">
         <v>0</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="12">
         <v>4</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="13">
         <f>IFERROR(C45/D45,0)</f>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="12">
         <f>IF(C45=0,"Missing",IF(C45=1,"Aware",IF(C45=2,"Partial",IF(C45=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="12">
         <f>IF(C45&lt;=1,"FIX",IF(C45=2,"Improve",""))</f>
       </c>
-      <c r="H45" s="12" t="s">
-        <v>45</v>
+      <c r="H45" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" s="9">
+      <c r="B46" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="11">
         <v>0</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="12">
         <v>4</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="13">
         <f>IFERROR(C46/D46,0)</f>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="12">
         <f>IF(C46=0,"Missing",IF(C46=1,"Aware",IF(C46=2,"Partial",IF(C46=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="12">
         <f>IF(C46&lt;=1,"FIX",IF(C46=2,"Improve",""))</f>
       </c>
-      <c r="H46" s="12" t="s">
-        <v>45</v>
+      <c r="H46" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" s="9">
+      <c r="B47" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="11">
         <v>0</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="12">
         <v>4</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="13">
         <f>IFERROR(C47/D47,0)</f>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="12">
         <f>IF(C47=0,"Missing",IF(C47=1,"Aware",IF(C47=2,"Partial",IF(C47=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="12">
         <f>IF(C47&lt;=1,"FIX",IF(C47=2,"Improve",""))</f>
       </c>
-      <c r="H47" s="12" t="s">
-        <v>45</v>
+      <c r="H47" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="9">
+      <c r="B48" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="11">
         <v>0</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="12">
         <v>4</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="13">
         <f>IFERROR(C48/D48,0)</f>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="12">
         <f>IF(C48=0,"Missing",IF(C48=1,"Aware",IF(C48=2,"Partial",IF(C48=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="12">
         <f>IF(C48&lt;=1,"FIX",IF(C48=2,"Improve",""))</f>
       </c>
-      <c r="H48" s="12" t="s">
-        <v>45</v>
+      <c r="H48" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C49" s="9">
+      <c r="B49" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="11">
         <v>0</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="12">
         <v>4</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="13">
         <f>IFERROR(C49/D49,0)</f>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="12">
         <f>IF(C49=0,"Missing",IF(C49=1,"Aware",IF(C49=2,"Partial",IF(C49=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="12">
         <f>IF(C49&lt;=1,"FIX",IF(C49=2,"Improve",""))</f>
       </c>
-      <c r="H49" s="12" t="s">
-        <v>45</v>
+      <c r="H49" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" s="9">
+      <c r="B50" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="11">
         <v>0</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="12">
         <v>4</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="13">
         <f>IFERROR(C50/D50,0)</f>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="12">
         <f>IF(C50=0,"Missing",IF(C50=1,"Aware",IF(C50=2,"Partial",IF(C50=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="12">
         <f>IF(C50&lt;=1,"FIX",IF(C50=2,"Improve",""))</f>
       </c>
-      <c r="H50" s="12" t="s">
-        <v>45</v>
+      <c r="H50" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="13">
+      <c r="B51" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="15">
         <f>SUM(C45:C50)</f>
       </c>
-      <c r="D51" s="13">
+      <c r="D51" s="15">
         <f>SUM(D45:D50)</f>
       </c>
-      <c r="E51" s="14">
+      <c r="E51" s="16">
         <f>IFERROR(C51/D51,0)</f>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="15">
         <f>IF(E51&gt;=0.85,"Optimized",IF(E51&gt;=0.70,"Strong",IF(E51&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="15">
         <f>IF(E51&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H51" s="15" t="s">
-        <v>45</v>
+      <c r="H51" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+      <c r="B52" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
     </row>
     <row r="53" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="9">
+      <c r="B53" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="11">
         <v>0</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="12">
         <v>4</v>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="13">
         <f>IFERROR(C53/D53,0)</f>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="12">
         <f>IF(C53=0,"Missing",IF(C53=1,"Aware",IF(C53=2,"Partial",IF(C53=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="12">
         <f>IF(C53&lt;=1,"FIX",IF(C53=2,"Improve",""))</f>
       </c>
-      <c r="H53" s="12" t="s">
-        <v>45</v>
+      <c r="H53" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" s="9">
+      <c r="B54" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="11">
         <v>0</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="12">
         <v>4</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="13">
         <f>IFERROR(C54/D54,0)</f>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="12">
         <f>IF(C54=0,"Missing",IF(C54=1,"Aware",IF(C54=2,"Partial",IF(C54=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="12">
         <f>IF(C54&lt;=1,"FIX",IF(C54=2,"Improve",""))</f>
       </c>
-      <c r="H54" s="12" t="s">
-        <v>45</v>
+      <c r="H54" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C55" s="9">
+      <c r="B55" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="11">
         <v>0</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="12">
         <v>4</v>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="13">
         <f>IFERROR(C55/D55,0)</f>
       </c>
-      <c r="F55" s="10">
+      <c r="F55" s="12">
         <f>IF(C55=0,"Missing",IF(C55=1,"Aware",IF(C55=2,"Partial",IF(C55=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="12">
         <f>IF(C55&lt;=1,"FIX",IF(C55=2,"Improve",""))</f>
       </c>
-      <c r="H55" s="12" t="s">
-        <v>45</v>
+      <c r="H55" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="9">
+      <c r="B56" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="11">
         <v>0</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="12">
         <v>4</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="13">
         <f>IFERROR(C56/D56,0)</f>
       </c>
-      <c r="F56" s="10">
+      <c r="F56" s="12">
         <f>IF(C56=0,"Missing",IF(C56=1,"Aware",IF(C56=2,"Partial",IF(C56=3,"Consistent","Documented"))))</f>
       </c>
-      <c r="G56" s="10">
+      <c r="G56" s="12">
         <f>IF(C56&lt;=1,"FIX",IF(C56=2,"Improve",""))</f>
       </c>
-      <c r="H56" s="12" t="s">
-        <v>45</v>
+      <c r="H56" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" s="13">
+      <c r="B57" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="15">
         <f>SUM(C53:C56)</f>
       </c>
-      <c r="D57" s="13">
+      <c r="D57" s="15">
         <f>SUM(D53:D56)</f>
       </c>
-      <c r="E57" s="14">
+      <c r="E57" s="16">
         <f>IFERROR(C57/D57,0)</f>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="15">
         <f>IF(E57&gt;=0.85,"Optimized",IF(E57&gt;=0.70,"Strong",IF(E57&gt;=0.40,"Progressing","Developing")))</f>
       </c>
-      <c r="G57" s="13">
+      <c r="G57" s="15">
         <f>IF(E57&lt;0.40,"PRIORITY","")</f>
       </c>
-      <c r="H57" s="15" t="s">
-        <v>45</v>
+      <c r="H57" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
+      <c r="B58" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3744,28 +3893,28 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C10">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C13:C18">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C21:C26">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C29:C34">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C37:C42">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C45:C50">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C5:C10">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="Score must be 0-4" error="Pick a value between 0 and 4 from the dropdown." sqref="C53:C56">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>MaturityScore</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3777,7 +3926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3796,368 +3945,368 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>106</v>
+      <c r="B3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="11">
+      <c r="B4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="13">
         <v>0.15</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="13">
         <f>'Self-Audit'!E11</f>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="19">
         <f>C4*D4</f>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="13">
         <v>0.75</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="13">
         <f>F4-D4</f>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="20">
         <f>IF(D4&lt;0.40,"Build agency target list; set SAM.gov alerts; pull FPDS incumbent data on top 5 contracts.","On track — maintain")</f>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="B5" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="13">
         <v>0.2</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="13">
         <f>'Self-Audit'!E19</f>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="19">
         <f>C5*D5</f>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="13">
         <v>0.75</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="13">
         <f>F5-D5</f>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>IF(D5&lt;0.40,"Implement a stage-gate capture process; start pursuits at 6+ months pre-RFP; require PWin per row.","On track — maintain")</f>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="B6" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="13">
         <v>0.15</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="13">
         <f>'Self-Audit'!E27</f>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="19">
         <f>C6*D6</f>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="13">
         <v>0.75</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="13">
         <f>F6-D6</f>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>IF(D6&lt;0.40,"Book 2 OSDBU briefings this quarter; attend industry days consistently; build 2 prime relationships.","On track — maintain")</f>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="B7" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="13">
         <v>0.2</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="13">
         <f>'Self-Audit'!E35</f>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="19">
         <f>C7*D7</f>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="13">
         <v>0.75</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="13">
         <f>F7-D7</f>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <f>IF(D7&lt;0.40,"Install color team reviews; build a Section L/M compliance matrix template; price to win, not to margin.","On track — maintain")</f>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="B8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="13">
         <v>0.15</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="13">
         <f>'Self-Audit'!E43</f>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <f>C8*D8</f>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="13">
         <v>0.75</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="13">
         <f>F8-D8</f>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="20">
         <f>IF(D8&lt;0.40,"Build 5 structured PP write-ups (CPARS format); collect every CPARS score on file.","On track — maintain")</f>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="11">
+      <c r="B9" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="13">
         <v>0.1</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="13">
         <f>'Self-Audit'!E51</f>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="19">
         <f>C9*D9</f>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="13">
         <v>0.75</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="13">
         <f>F9-D9</f>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>IF(D9&lt;0.40,"Renew SAM; verify certifications; document COI process; review NAICS size standards.","On track — maintain")</f>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="13">
         <v>0.05</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="13">
         <f>'Self-Audit'!E57</f>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="19">
         <f>C10*D10</f>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="13">
         <v>0.75</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="13">
         <f>F10-D10</f>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="20">
         <f>IF(D10&lt;0.40,"Write the BD strategy; install a CRM; refresh the capability statement per top agency.","On track — maintain")</f>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="14">
+      <c r="B11" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="16">
         <f>SUM(C4:C10)</f>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="16">
         <f>SUMPRODUCT(C4:C10,D4:D10)/SUM(C4:C10)</f>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="21">
         <f>SUM(E4:E10)</f>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="16">
         <f>0.75</f>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="16">
         <f>F11-D11</f>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="22">
         <f>IF(D11&gt;=0.85,"Optimized — keep refining",IF(D11&gt;=0.70,"Strong — work the gaps",IF(D11&gt;=0.40,"Progressing — pick 3 priorities","Developing — work the 30-day plan")))</f>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="B13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="B14" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="B15" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="B16" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="B17" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="19" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="23">
+      <c r="B19" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25">
         <f>IF(D11&gt;=0.85,"OPTIMIZED",IF(D11&gt;=0.70,"STRONG",IF(D11&gt;=0.40,"PROGRESSING","DEVELOPING")))</f>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="B21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="18">
+      <c r="B22" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="20">
         <f>INDEX(B4:B10,MATCH(SMALL(D4:D10,1),D4:D10,0))</f>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="13">
         <f>SMALL(D4:D10,1)</f>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="20">
         <f>INDEX(H4:H10,MATCH(SMALL(D4:D10,1),D4:D10,0))</f>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="18">
+      <c r="B23" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="20">
         <f>INDEX(B4:B10,MATCH(SMALL(D4:D10,2),D4:D10,0))</f>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="13">
         <f>SMALL(D4:D10,2)</f>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="20">
         <f>INDEX(H4:H10,MATCH(SMALL(D4:D10,2),D4:D10,0))</f>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
     </row>
     <row r="24" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="18">
+      <c r="B24" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="20">
         <f>INDEX(B4:B10,MATCH(SMALL(D4:D10,3),D4:D10,0))</f>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="13">
         <f>SMALL(D4:D10,3)</f>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="20">
         <f>INDEX(H4:H10,MATCH(SMALL(D4:D10,3),D4:D10,0))</f>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4267,7 +4416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4285,606 +4434,606 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>140</v>
+      <c r="B3" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I4" s="10">
+      <c r="B4" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="12">
         <f>IF(H4="Complete","Yes","")</f>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I5" s="10">
+      <c r="B5" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="28"/>
+      <c r="G5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="12">
         <f>IF(H5="Complete","Yes","")</f>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I6" s="10">
+      <c r="B6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="G6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="12">
         <f>IF(H6="Complete","Yes","")</f>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I7" s="10">
+      <c r="B7" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="28"/>
+      <c r="G7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="12">
         <f>IF(H7="Complete","Yes","")</f>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I8" s="10">
+      <c r="B8" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="12">
         <f>IF(H8="Complete","Yes","")</f>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I9" s="10">
+      <c r="B9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="28"/>
+      <c r="G9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="12">
         <f>IF(H9="Complete","Yes","")</f>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I10" s="10">
+      <c r="B10" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="12">
         <f>IF(H10="Complete","Yes","")</f>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I11" s="10">
+      <c r="B11" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="12">
         <f>IF(H11="Complete","Yes","")</f>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I12" s="10">
+      <c r="B12" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="12">
         <f>IF(H12="Complete","Yes","")</f>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="28"/>
+      <c r="G13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="12">
+        <f>IF(H13="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="28"/>
+      <c r="G14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="12">
+        <f>IF(H14="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="28"/>
+      <c r="G15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="12">
+        <f>IF(H15="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="28"/>
+      <c r="G16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="12">
+        <f>IF(H16="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="12">
+        <f>IF(H17="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I13" s="10">
-        <f>IF(H13="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="10">
-        <f>IF(H14="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="D18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="12">
+        <f>IF(H18="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="12">
+        <f>IF(H19="Complete","Yes","")</f>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="10">
-        <f>IF(H15="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="26"/>
-      <c r="G16" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="10">
-        <f>IF(H16="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I17" s="10">
-        <f>IF(H17="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="26"/>
-      <c r="G18" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I18" s="10">
-        <f>IF(H18="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="26"/>
-      <c r="G19" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="10">
-        <f>IF(H19="Complete","Yes","")</f>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="10">
+      <c r="D20" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" s="12">
         <f>IF(H20="Complete","Yes","")</f>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="10">
+      <c r="D21" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="28"/>
+      <c r="G21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="12">
         <f>IF(H21="Complete","Yes","")</f>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="B23" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C24" s="27">
+      <c r="B24" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="29">
         <f>COUNTA(B4:B21)</f>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="D24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" s="27">
+      <c r="B25" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="29">
         <f>COUNTIF(H4:H21,"Complete")</f>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="D25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="27">
+      <c r="B26" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="29">
         <f>COUNTIF(H4:H21,"In Progress")</f>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="D26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="C27" s="27">
+      <c r="B27" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="29">
         <f>COUNTIF(H4:H21,"Blocked")</f>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="D27" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="27">
+      <c r="B28" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="29">
         <f>COUNTIF(H4:H21,"Not Started")</f>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="D28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="C29" s="28">
+      <c r="B29" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="30">
         <f>IFERROR(COUNTIF(H4:H21,"Complete")/COUNTA(B4:B21),0)</f>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="D29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="31" ht="28" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
+      <c r="B31" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5099,22 +5248,22 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation type="list" sqref="D10:D21">
-      <formula1>"30 days,60 days,90 days"</formula1>
+      <formula1>ActionWindow</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D4:D21">
-      <formula1>"30 days,60 days,90 days"</formula1>
+      <formula1>ActionWindow</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="G10:G21">
-      <formula1>"Critical,High,Medium,Low"</formula1>
+      <formula1>PriorityLevel</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="G4:G21">
-      <formula1>"Critical,High,Medium,Low"</formula1>
+      <formula1>PriorityLevel</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H10:H21">
-      <formula1>"Not Started,In Progress,Blocked,Complete"</formula1>
+      <formula1>TaskStatus</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H4:H21">
-      <formula1>"Not Started,In Progress,Blocked,Complete"</formula1>
+      <formula1>TaskStatus</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5126,7 +5275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5140,142 +5289,142 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>183</v>
+      <c r="B3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>185</v>
+      <c r="B4" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>187</v>
+      <c r="B5" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>190</v>
+      <c r="B6" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>192</v>
+      <c r="B7" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>194</v>
+      <c r="B8" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>196</v>
+      <c r="B9" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>198</v>
+      <c r="B10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D13" s="3"/>
+      <c r="B13" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" s="3"/>
+      <c r="B14" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" ht="36" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D15" s="3"/>
+      <c r="B15" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" ht="36" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="3"/>
+      <c r="B16" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="6">
